--- a/data/BÁO CÁO CƠ SỞ DỮ LIỆU TỔNG LỰC_ DỰ ÁN NY'AH PHÚ ĐỊNH.xlsx
+++ b/data/BÁO CÁO CƠ SỞ DỮ LIỆU TỔNG LỰC_ DỰ ÁN NY'AH PHÚ ĐỊNH.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QuangLêBáDuy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhadatcompany.sharepoint.com/sites/TeamMktg/Shared Documents/NPD mktg/mktg - private/03_Content/ChatBot, LiveSlide/ChatBotData_Upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75F365C-F455-4DDB-B3AE-FDF802A7F0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{B75F365C-F455-4DDB-B3AE-FDF802A7F0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA7DAD51-1F5E-41A8-B95A-78DBE1FBE4CC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="129">
   <si>
     <t>Thông số</t>
   </si>
@@ -37,9 +37,6 @@
     <t>3,756.5 m2</t>
   </si>
   <si>
-    <t>Tổng số sản phẩm</t>
-  </si>
-  <si>
     <t>50 căn</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>Thời gian bàn giao</t>
   </si>
   <si>
-    <t>Dự kiến năm 2024 (Sổ hồng dự kiến tháng 10/2024)</t>
-  </si>
-  <si>
     <t>Hạng mục</t>
   </si>
   <si>
@@ -313,19 +307,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Chủ đầu tư &amp; Đơn vị phát triển:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Nhã Đạt là đơn vị phát triển và xây dựng với hơn 20 năm kinh nghiệm.</t>
-    </r>
-  </si>
-  <si>
     <t>2. CHI TIẾT CÁC MẪU NHÀ ĐẶC TRƯNG</t>
   </si>
   <si>
@@ -342,32 +323,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Mẫu Cosmo:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Mẫu nhà phố cao cấp nhất với mặt tiền rộng 5 mét. Diện tích sử dụng 175m2, nổi bật với phòng ngủ Master rộng 38m2.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mẫu Opus:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Dòng nhà phố thương mại hạng A "2 trong 1", tối ưu cho khởi nghiệp và kinh doanh. Diện tích sử dụng 270m2 với 2 tầng chuyên dụng cho kinh doanh.</t>
-    </r>
-  </si>
-  <si>
     <t>3. QUY CÁCH XÂY DỰNG &amp; VẬT LIỆU KỸ THUẬT</t>
   </si>
   <si>
@@ -385,19 +340,6 @@
   </si>
   <si>
     <r>
-      <t>Vật liệu chính:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Gạch tuynel tiêu chuẩn Đồng Nai/Bình Dương; Thép Miền Nam/Pomina; Xi măng Hà Tiên/Holcim; Bê tông tươi thương phẩm M250.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Chiều cao tầng:</t>
     </r>
     <r>
@@ -445,32 +387,6 @@
   </si>
   <si>
     <r>
-      <t>Khu vực Bếp:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Tủ bếp trên/dưới ván An Cường, quầy bar, trọn bộ thiết bị cao cấp gồm bếp từ 3 vùng nấu, máy hút mùi, lò vi sóng kết hợp nướng, máy rửa chén, tủ lạnh, máy giặt/sấy.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Hệ thống lạnh:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Lắp sẵn máy lạnh LG âm trần cho phòng ngủ và treo tường cho phòng khách/bếp.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Công nghệ:</t>
     </r>
     <r>
@@ -483,19 +399,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Nội thất đồ gỗ:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Tủ quần áo MFC kháng ẩm trong các phòng ngủ có đèn led tự động, kệ Tivi, vách ngăn trang trí và các kệ tường trang trí khác.</t>
-    </r>
-  </si>
-  <si>
     <t>5. HỆ THỐNG CÔNG NGHỆ ĐỘC QUYỀN</t>
   </si>
   <si>
@@ -567,63 +470,6 @@
   </si>
   <si>
     <t>Chính sách chiết khấu thanh toán nhanh:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Gói Max: Chiết khấu gấp </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>6 lần</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> lãi suất tiết kiệm 9 tháng của Vietcombank.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Gói Air: Chiết khấu gấp </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>5 lần</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> lãi suất tiết kiệm 9 tháng của Vietcombank.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ngân hàng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> BIDV và Vietcombank hỗ trợ cho vay tối đa 50% giá trị căn nhà.</t>
-    </r>
   </si>
   <si>
     <t>7. PHÁP LÝ &amp; BẢO HÀNH</t>
@@ -722,6 +568,119 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Tài liệu này được sử dụng làm cơ sở dữ liệu chính để trả lời mọi thắc mắc của khách hàng về dự án Ny'ah Phú Định. Khi trả lời, bot cần ưu tiên các thông số kỹ thuật và chính sách tài chính đã liệt kê ở trên.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tổng số căn nhà</t>
+  </si>
+  <si>
+    <t>Dự kiến năm 2025</t>
+  </si>
+  <si>
+    <r>
+      <t>Chủ đầu tư &amp; Đơn vị phát triển:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Nhã Đạt là đơn vị phát triển và xây dựng với hơn 20 năm kinh nghiệm phát triển bất động sản</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mẫu Cosmo gen 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Mẫu nhà phố siêu sáng với mặt tiền 5 mét. Diện tích sử dụng 175m2, nổi bật với phòng ngủ Master rộng 38m2.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mẫu Opus:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Dòng nhà phố thương mại "2 trong 1", tối ưu cho khởi nghiệp kinh doanh và an cư. Diện tích sử dụng 270m2 với 2 tầng chuyên dụng cho kinh doanh.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vật liệu xây dựng chính:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Gạch tuynel tiêu chuẩn Đồng Nai/Bình Dương; Thép Miền Nam/Pomina; Xi măng Hà Tiên/Holcim; Bê tông tươi thương phẩm M250.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Khu vực Bếp:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Tủ bếp trên/dưới ván An Cường, quầy bar. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hệ thống lạnh:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Lắp sẵn máy lạnh LG âm trần cho các phòng ngủ và treo tường cho phòng khách/bếp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nội thất: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>kệ Tivi, vách ngăn trang trí và các kệ tường trang trí khác.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanh toán ngay 85% - công chứng sang tên ngay. Tặng ngay thang máy khi mua nhà </t>
+  </si>
+  <si>
+    <r>
+      <t>Ngân hàng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> BIDV và Vietcombank hỗ trợ cho vay tối đa 70% giá trị căn nhà.</t>
     </r>
   </si>
 </sst>
@@ -769,12 +728,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -789,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -811,6 +776,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1030,9 +999,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B75"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="12.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +1009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="12.5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1048,46 +1017,46 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="12.5">
       <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="12.5">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="12.5">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="12.5">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1">
@@ -1095,27 +1064,27 @@
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" customHeight="1">
@@ -1123,22 +1092,22 @@
     </row>
     <row r="19" spans="1:1" ht="15.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.75" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.75" customHeight="1">
@@ -1146,32 +1115,32 @@
     </row>
     <row r="25" spans="1:1" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.75" customHeight="1">
@@ -1179,52 +1148,52 @@
     </row>
     <row r="33" spans="1:1" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.75" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A40" s="7" t="s">
-        <v>105</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.75" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.75" customHeight="1">
@@ -1232,22 +1201,22 @@
     </row>
     <row r="45" spans="1:1" ht="15.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15.75" customHeight="1">
@@ -1255,52 +1224,50 @@
     </row>
     <row r="51" spans="1:1" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15.75" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="15.75" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="15.75" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="15.75" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="15.75" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A58" s="6" t="s">
-        <v>119</v>
-      </c>
+      <c r="A58" s="6"/>
     </row>
     <row r="59" spans="1:1" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15.75" customHeight="1">
@@ -1308,22 +1275,22 @@
     </row>
     <row r="63" spans="1:1" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="15.75" customHeight="1">
@@ -1331,22 +1298,22 @@
     </row>
     <row r="69" spans="1:1" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.75" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1361,78 +1328,78 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1446,149 +1413,149 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1602,146 +1569,146 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2025,13 +1992,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E356476-5B4A-46DA-BFD0-0A7FB683E199}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E356476-5B4A-46DA-BFD0-0A7FB683E199}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="300fa37b-2a09-4011-a0db-c11ba6d392f7"/>
+    <ds:schemaRef ds:uri="a16b777b-eb0b-4844-aa73-ac2af43907aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{752C11FE-0148-45F2-A26D-EC899B6FFDEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{752C11FE-0148-45F2-A26D-EC899B6FFDEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A92222AC-0296-49AE-9154-31A0C972EB7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A92222AC-0296-49AE-9154-31A0C972EB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a16b777b-eb0b-4844-aa73-ac2af43907aa"/>
+    <ds:schemaRef ds:uri="300fa37b-2a09-4011-a0db-c11ba6d392f7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>